--- a/Mentor-III-CSE-B.xlsx
+++ b/Mentor-III-CSE-B.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Downloads\Fw_ Mentor Mentee Allocation- 2026-2027 ODD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\FREE LANCING\od system\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB3D8A7C-08FA-4B70-A6AF-8ED6C11D803F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01F58CA6-B588-4B07-B249-39631A279BF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1848" yWindow="1848" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="III CSE B" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="168">
   <si>
     <t>REGISTER NUMBER</t>
   </si>
@@ -523,6 +523,15 @@
   </si>
   <si>
     <t>HOD NAME</t>
+  </si>
+  <si>
+    <t>GENDER</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>M</t>
   </si>
 </sst>
 </file>
@@ -965,7 +974,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H72"/>
+  <dimension ref="A2:I72"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="11" customWidth="1"/>
@@ -976,10 +985,11 @@
     <col min="6" max="6" width="18.5546875" style="11" customWidth="1"/>
     <col min="7" max="7" width="28.21875" style="11" customWidth="1"/>
     <col min="8" max="8" width="27.21875" style="11" customWidth="1"/>
-    <col min="9" max="16384" width="9.109375" style="11"/>
+    <col min="9" max="9" width="16.5546875" style="11" customWidth="1"/>
+    <col min="10" max="16384" width="9.109375" style="11"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1004,8 +1014,11 @@
       <c r="H2" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I2" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>1</v>
       </c>
@@ -1030,8 +1043,11 @@
       <c r="H3" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I3" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>2</v>
       </c>
@@ -1056,8 +1072,11 @@
       <c r="H4" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I4" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>3</v>
       </c>
@@ -1082,8 +1101,11 @@
       <c r="H5" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I5" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>4</v>
       </c>
@@ -1108,8 +1130,11 @@
       <c r="H6" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I6" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>5</v>
       </c>
@@ -1134,8 +1159,11 @@
       <c r="H7" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I7" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>6</v>
       </c>
@@ -1160,8 +1188,11 @@
       <c r="H8" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I8" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>7</v>
       </c>
@@ -1186,8 +1217,11 @@
       <c r="H9" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I9" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>8</v>
       </c>
@@ -1212,8 +1246,11 @@
       <c r="H10" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I10" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>9</v>
       </c>
@@ -1238,8 +1275,11 @@
       <c r="H11" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I11" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>10</v>
       </c>
@@ -1264,8 +1304,11 @@
       <c r="H12" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I12" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>11</v>
       </c>
@@ -1290,8 +1333,11 @@
       <c r="H13" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I13" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>12</v>
       </c>
@@ -1316,8 +1362,11 @@
       <c r="H14" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I14" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>13</v>
       </c>
@@ -1342,8 +1391,11 @@
       <c r="H15" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I15" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>14</v>
       </c>
@@ -1368,8 +1420,11 @@
       <c r="H16" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I16" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>15</v>
       </c>
@@ -1394,8 +1449,11 @@
       <c r="H17" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I17" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>16</v>
       </c>
@@ -1420,8 +1478,11 @@
       <c r="H18" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I18" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>17</v>
       </c>
@@ -1446,8 +1507,11 @@
       <c r="H19" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I19" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>18</v>
       </c>
@@ -1472,8 +1536,11 @@
       <c r="H20" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I20" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>19</v>
       </c>
@@ -1498,8 +1565,11 @@
       <c r="H21" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I21" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>20</v>
       </c>
@@ -1524,8 +1594,11 @@
       <c r="H22" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I22" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>21</v>
       </c>
@@ -1550,8 +1623,11 @@
       <c r="H23" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I23" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>22</v>
       </c>
@@ -1576,8 +1652,11 @@
       <c r="H24" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I24" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>23</v>
       </c>
@@ -1602,8 +1681,11 @@
       <c r="H25" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I25" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>24</v>
       </c>
@@ -1628,8 +1710,11 @@
       <c r="H26" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I26" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>25</v>
       </c>
@@ -1654,8 +1739,11 @@
       <c r="H27" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I27" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>26</v>
       </c>
@@ -1680,8 +1768,11 @@
       <c r="H28" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I28" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>27</v>
       </c>
@@ -1706,8 +1797,11 @@
       <c r="H29" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I29" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>28</v>
       </c>
@@ -1732,8 +1826,11 @@
       <c r="H30" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I30" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>29</v>
       </c>
@@ -1758,8 +1855,11 @@
       <c r="H31" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I31" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>30</v>
       </c>
@@ -1784,8 +1884,11 @@
       <c r="H32" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I32" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>31</v>
       </c>
@@ -1810,8 +1913,11 @@
       <c r="H33" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I33" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
         <v>32</v>
       </c>
@@ -1836,8 +1942,11 @@
       <c r="H34" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I34" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>33</v>
       </c>
@@ -1862,8 +1971,11 @@
       <c r="H35" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I35" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
         <v>34</v>
       </c>
@@ -1888,8 +2000,11 @@
       <c r="H36" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I36" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
         <v>35</v>
       </c>
@@ -1914,8 +2029,11 @@
       <c r="H37" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I37" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
         <v>36</v>
       </c>
@@ -1940,8 +2058,11 @@
       <c r="H38" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I38" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>37</v>
       </c>
@@ -1966,8 +2087,11 @@
       <c r="H39" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I39" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
         <v>38</v>
       </c>
@@ -1992,8 +2116,11 @@
       <c r="H40" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I40" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>39</v>
       </c>
@@ -2018,8 +2145,11 @@
       <c r="H41" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I41" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
         <v>40</v>
       </c>
@@ -2044,8 +2174,11 @@
       <c r="H42" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I42" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
         <v>41</v>
       </c>
@@ -2070,8 +2203,11 @@
       <c r="H43" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I43" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
         <v>42</v>
       </c>
@@ -2096,8 +2232,11 @@
       <c r="H44" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I44" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
         <v>43</v>
       </c>
@@ -2122,8 +2261,11 @@
       <c r="H45" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I45" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="4">
         <v>44</v>
       </c>
@@ -2148,8 +2290,11 @@
       <c r="H46" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I46" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
         <v>45</v>
       </c>
@@ -2174,8 +2319,11 @@
       <c r="H47" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I47" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="4">
         <v>46</v>
       </c>
@@ -2200,8 +2348,11 @@
       <c r="H48" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I48" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="4">
         <v>47</v>
       </c>
@@ -2226,8 +2377,11 @@
       <c r="H49" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I49" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="4">
         <v>48</v>
       </c>
@@ -2252,8 +2406,11 @@
       <c r="H50" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I50" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="4">
         <v>49</v>
       </c>
@@ -2278,8 +2435,11 @@
       <c r="H51" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I51" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="4">
         <v>50</v>
       </c>
@@ -2304,8 +2464,11 @@
       <c r="H52" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I52" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="4">
         <v>51</v>
       </c>
@@ -2330,8 +2493,11 @@
       <c r="H53" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I53" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="4">
         <v>52</v>
       </c>
@@ -2356,8 +2522,11 @@
       <c r="H54" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I54" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="4">
         <v>53</v>
       </c>
@@ -2382,8 +2551,11 @@
       <c r="H55" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I55" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="4">
         <v>54</v>
       </c>
@@ -2408,8 +2580,11 @@
       <c r="H56" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I56" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="4">
         <v>55</v>
       </c>
@@ -2434,8 +2609,11 @@
       <c r="H57" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I57" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="4">
         <v>56</v>
       </c>
@@ -2460,8 +2638,11 @@
       <c r="H58" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I58" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="4">
         <v>57</v>
       </c>
@@ -2486,8 +2667,11 @@
       <c r="H59" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I59" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="4">
         <v>58</v>
       </c>
@@ -2512,8 +2696,11 @@
       <c r="H60" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I60" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="4">
         <v>59</v>
       </c>
@@ -2538,8 +2725,11 @@
       <c r="H61" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I61" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="4">
         <v>60</v>
       </c>
@@ -2564,8 +2754,11 @@
       <c r="H62" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I62" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="4">
         <v>61</v>
       </c>
@@ -2588,8 +2781,11 @@
       <c r="H63" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I63" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="4">
         <v>62</v>
       </c>
@@ -2612,8 +2808,11 @@
       <c r="H64" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I64" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="15">
         <v>63</v>
       </c>
@@ -2636,8 +2835,11 @@
       <c r="H65" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I65" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="15">
         <v>64</v>
       </c>
@@ -2660,24 +2862,27 @@
       <c r="H66" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I66" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E67" s="14"/>
       <c r="G67" s="12"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E68" s="14"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E69" s="14"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E70" s="14"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E71" s="14"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E72" s="14"/>
     </row>
   </sheetData>
